--- a/Win32/Debug/Template.xlsx
+++ b/Win32/Debug/Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Embarcadero\Studio\Projects\Salary\Win32\Debug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC72296-0911-4B22-AA3A-242F9CEAA3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D2DD43-791A-4D37-85C9-EAEC46EBCD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Таб. №</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>К выдаче</t>
-  </si>
-  <si>
-    <t>Ведомость начисления зарплаты</t>
   </si>
 </sst>
 </file>
@@ -75,7 +72,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -83,12 +80,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -369,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A3:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -380,34 +393,29 @@
     <col min="6" max="8" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Win32/Debug/Template.xlsx
+++ b/Win32/Debug/Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Embarcadero\Studio\Projects\Salary\Win32\Debug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D2DD43-791A-4D37-85C9-EAEC46EBCD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137B0AD3-E9EA-44AC-9A09-90B055B5E4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,12 +55,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -99,9 +108,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -382,40 +392,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:H3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
     <col min="3" max="3" width="15.28515625" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="8" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
